--- a/Dataset.xlsx
+++ b/Dataset.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://atpglobal-my.sharepoint.com/personal/silvialin_tw_atpinc_com/Documents/桌面/HR/薪資結構整理/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="11_F25DC773A252ABDACC104809C95E6ED45ADE58FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9DD0AA9-0FFB-4F39-A1D3-14AEEF2369B5}"/>
+  <xr:revisionPtr revIDLastSave="286" documentId="11_F25DC773A252ABDACC104809C95E6ED45ADE58FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2FF8DD8-76BA-4BC1-81A1-C8F8D4D3939F}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="GovData" sheetId="1" r:id="rId1"/>
+    <sheet name="104" sheetId="3" state="hidden" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="206">
   <si>
     <t>Job_Title</t>
   </si>
@@ -313,6 +314,387 @@
   </si>
   <si>
     <t>39,709</t>
+  </si>
+  <si>
+    <t>104_Offer_Avg</t>
+  </si>
+  <si>
+    <t>監督人員(含現場及辦公室主任、科/股長)</t>
+  </si>
+  <si>
+    <t>品管、工管及生管工程師</t>
+  </si>
+  <si>
+    <t>會計人員</t>
+  </si>
+  <si>
+    <t>楠梓電子股份有限公司</t>
+  </si>
+  <si>
+    <t>早班12H-督導員H003</t>
+  </si>
+  <si>
+    <t>倉儲管理員</t>
+  </si>
+  <si>
+    <t>固也泰電子工業有限公司</t>
+  </si>
+  <si>
+    <t>生產課長</t>
+  </si>
+  <si>
+    <t>克瑞電子股份有限公司</t>
+  </si>
+  <si>
+    <t>製造組長/班長</t>
+  </si>
+  <si>
+    <t>月薪42,000元以上</t>
+  </si>
+  <si>
+    <t>加高電子股份有限公司</t>
+  </si>
+  <si>
+    <t>輝創電子股份有限公司</t>
+  </si>
+  <si>
+    <t>產線副班長</t>
+  </si>
+  <si>
+    <t>月薪30,000元以上</t>
+  </si>
+  <si>
+    <t>品保工程師</t>
+  </si>
+  <si>
+    <t>旺詮股份有限公司</t>
+  </si>
+  <si>
+    <t>生管人員</t>
+  </si>
+  <si>
+    <t>北極光電股份有限公司</t>
+  </si>
+  <si>
+    <t>品管工程師</t>
+  </si>
+  <si>
+    <t>生管/物控 工程師</t>
+  </si>
+  <si>
+    <t>組弘科技股份有限公司</t>
+  </si>
+  <si>
+    <t>品保-品管工程師</t>
+  </si>
+  <si>
+    <t>台郡科技股份有限公司(總公司)</t>
+  </si>
+  <si>
+    <t>會計專員</t>
+  </si>
+  <si>
+    <t>可恩迪股份有限公司</t>
+  </si>
+  <si>
+    <t>財務會計人員</t>
+  </si>
+  <si>
+    <t>月薪39,000元以上</t>
+  </si>
+  <si>
+    <t>艾新科環保材料有限公司</t>
+  </si>
+  <si>
+    <t>常珵科技股份有限公司</t>
+  </si>
+  <si>
+    <t>資深會計 Accountant</t>
+  </si>
+  <si>
+    <t>啟延電子科技股份有限公司</t>
+  </si>
+  <si>
+    <t>財務會計</t>
+  </si>
+  <si>
+    <t>政久興業股份有限公司</t>
+  </si>
+  <si>
+    <t>月薪29,500~34,400元
+31950</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>月薪29,500~32,000元
+30750</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>月薪50,000~60,000元
+55000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>月薪38,000~45,000元
+41500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>月薪30,000~32,000元
+31000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>月薪30,000~35,000元
+32500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>月薪38,000~41,000元
+39500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>月薪35,000~52,000元
+43500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>月薪40,000~50,000元
+45000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>月薪33,000~39,000元
+36000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>月薪46,000~50,000元
+48000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>月薪60,000~100,000元
+80000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>177,469</t>
+  </si>
+  <si>
+    <t>120,404</t>
+  </si>
+  <si>
+    <t>80,625</t>
+  </si>
+  <si>
+    <t>64,183</t>
+  </si>
+  <si>
+    <t>74,301</t>
+  </si>
+  <si>
+    <t>61,935</t>
+  </si>
+  <si>
+    <t>73,964</t>
+  </si>
+  <si>
+    <t>71,946</t>
+  </si>
+  <si>
+    <t>74,713</t>
+  </si>
+  <si>
+    <t>83,669</t>
+  </si>
+  <si>
+    <t>44,830</t>
+  </si>
+  <si>
+    <t>37,804</t>
+  </si>
+  <si>
+    <t>55,873</t>
+  </si>
+  <si>
+    <t>55,569</t>
+  </si>
+  <si>
+    <t>51,105</t>
+  </si>
+  <si>
+    <t>62,597</t>
+  </si>
+  <si>
+    <t>61,309</t>
+  </si>
+  <si>
+    <t>53,611</t>
+  </si>
+  <si>
+    <t>42,565</t>
+  </si>
+  <si>
+    <t>43,248</t>
+  </si>
+  <si>
+    <t>36,840</t>
+  </si>
+  <si>
+    <t>45,845</t>
+  </si>
+  <si>
+    <t>37,724</t>
+  </si>
+  <si>
+    <t>44,009</t>
+  </si>
+  <si>
+    <t>35,425</t>
+  </si>
+  <si>
+    <t>34,010</t>
+  </si>
+  <si>
+    <t>34,660</t>
+  </si>
+  <si>
+    <t>39,084</t>
+  </si>
+  <si>
+    <t>中階主管(經理)</t>
+  </si>
+  <si>
+    <t>電機、電子工程師</t>
+  </si>
+  <si>
+    <t>產品及服裝設計師(含工業設計)</t>
+  </si>
+  <si>
+    <t>會(審)計師</t>
+  </si>
+  <si>
+    <t>專案管理師(含經營管理顧問)</t>
+  </si>
+  <si>
+    <t>廣告及行銷專業人員(含企劃)</t>
+  </si>
+  <si>
+    <t>資訊及通訊專業人員(含系統分析、程式設計、資料庫及網路專業人員)</t>
+  </si>
+  <si>
+    <t>電機、電子技術員</t>
+  </si>
+  <si>
+    <t>品管、工管及生管技術員</t>
+  </si>
+  <si>
+    <t>工商業銷售代表(含業務員)</t>
+  </si>
+  <si>
+    <t>採購員</t>
+  </si>
+  <si>
+    <t>專業秘書</t>
+  </si>
+  <si>
+    <t>法務人員</t>
+  </si>
+  <si>
+    <t>資訊管理及維護技術員</t>
+  </si>
+  <si>
+    <t>總務</t>
+  </si>
+  <si>
+    <t>辦公室綜合事務人員(含資料登錄、一般事務秘書)</t>
+  </si>
+  <si>
+    <t>接待員及服務台事務人員(含總機)</t>
+  </si>
+  <si>
+    <t>會計助理、簿記、出納</t>
+  </si>
+  <si>
+    <t>存貨事務人員</t>
+  </si>
+  <si>
+    <t>生產及物料規劃事務人員</t>
+  </si>
+  <si>
+    <t>人事事務人員</t>
+  </si>
+  <si>
+    <t>生產機械設備操作人員、剪裁或裁縫人員</t>
+  </si>
+  <si>
+    <t>組裝(現場)人員</t>
+  </si>
+  <si>
+    <t>半導體製品產線作業人員</t>
+  </si>
+  <si>
+    <t>175,438</t>
+  </si>
+  <si>
+    <t>116,286</t>
+  </si>
+  <si>
+    <t>76,592</t>
+  </si>
+  <si>
+    <t>65,199</t>
+  </si>
+  <si>
+    <t>69,438</t>
+  </si>
+  <si>
+    <t>81,423</t>
+  </si>
+  <si>
+    <t>70,698</t>
+  </si>
+  <si>
+    <t>57,634</t>
+  </si>
+  <si>
+    <t>59,765</t>
+  </si>
+  <si>
+    <t>52,342</t>
+  </si>
+  <si>
+    <t>63,168</t>
+  </si>
+  <si>
+    <t>59,502</t>
+  </si>
+  <si>
+    <t>49,931</t>
+  </si>
+  <si>
+    <t>43,964</t>
+  </si>
+  <si>
+    <t>44,963</t>
+  </si>
+  <si>
+    <t>40,720</t>
+  </si>
+  <si>
+    <t>45,660</t>
+  </si>
+  <si>
+    <t>37,556</t>
+  </si>
+  <si>
+    <t>40,151</t>
+  </si>
+  <si>
+    <t>35,215</t>
   </si>
 </sst>
 </file>
@@ -350,12 +732,21 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -365,8 +756,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{BAF5389D-7812-4681-8280-3DB5022A5555}"/>
@@ -386,8 +785,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E58A41AD-D827-4DE6-8F9C-F6740B6F0CDC}" name="表格1" displayName="表格1" ref="A1:C57" totalsRowShown="0">
-  <autoFilter ref="A1:C57" xr:uid="{E58A41AD-D827-4DE6-8F9C-F6740B6F0CDC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E58A41AD-D827-4DE6-8F9C-F6740B6F0CDC}" name="表格1" displayName="表格1" ref="A1:C113" totalsRowShown="0">
+  <autoFilter ref="A1:C113" xr:uid="{E58A41AD-D827-4DE6-8F9C-F6740B6F0CDC}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{DC9E6555-46C4-4717-BCFA-E3226757A6C5}" name="Job_Title"/>
     <tableColumn id="4" xr3:uid="{321BD59F-ED72-4947-B0D6-0895CF8F3FCF}" name="Monthly_Salary"/>
@@ -660,7 +1059,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C113"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -977,13 +1376,13 @@
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="A29" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="3">
         <v>2024</v>
       </c>
     </row>
@@ -1285,14 +1684,630 @@
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+      <c r="A57" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C57">
-        <v>2023</v>
+      <c r="C57" s="3">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>3</v>
+      </c>
+      <c r="B58" t="s">
+        <v>134</v>
+      </c>
+      <c r="C58">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>4</v>
+      </c>
+      <c r="B59" t="s">
+        <v>135</v>
+      </c>
+      <c r="C59">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>5</v>
+      </c>
+      <c r="B60" t="s">
+        <v>136</v>
+      </c>
+      <c r="C60">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B61" t="s">
+        <v>137</v>
+      </c>
+      <c r="C61">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>12</v>
+      </c>
+      <c r="B62" t="s">
+        <v>138</v>
+      </c>
+      <c r="C62">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>139</v>
+      </c>
+      <c r="C63">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>16</v>
+      </c>
+      <c r="B64" t="s">
+        <v>140</v>
+      </c>
+      <c r="C64">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>20</v>
+      </c>
+      <c r="B65" t="s">
+        <v>141</v>
+      </c>
+      <c r="C65">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>21</v>
+      </c>
+      <c r="B66" t="s">
+        <v>142</v>
+      </c>
+      <c r="C66">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>22</v>
+      </c>
+      <c r="B67" t="s">
+        <v>143</v>
+      </c>
+      <c r="C67">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>41</v>
+      </c>
+      <c r="B68" t="s">
+        <v>144</v>
+      </c>
+      <c r="C68">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>42</v>
+      </c>
+      <c r="B69" t="s">
+        <v>145</v>
+      </c>
+      <c r="C69">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>43</v>
+      </c>
+      <c r="B70" t="s">
+        <v>146</v>
+      </c>
+      <c r="C70">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>44</v>
+      </c>
+      <c r="B71" t="s">
+        <v>147</v>
+      </c>
+      <c r="C71">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>45</v>
+      </c>
+      <c r="B72" t="s">
+        <v>148</v>
+      </c>
+      <c r="C72">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>46</v>
+      </c>
+      <c r="B73" t="s">
+        <v>149</v>
+      </c>
+      <c r="C73">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>47</v>
+      </c>
+      <c r="B74" t="s">
+        <v>150</v>
+      </c>
+      <c r="C74">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>48</v>
+      </c>
+      <c r="B75" t="s">
+        <v>151</v>
+      </c>
+      <c r="C75">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>49</v>
+      </c>
+      <c r="B76" t="s">
+        <v>152</v>
+      </c>
+      <c r="C76">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>50</v>
+      </c>
+      <c r="B77" t="s">
+        <v>153</v>
+      </c>
+      <c r="C77">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>51</v>
+      </c>
+      <c r="B78" t="s">
+        <v>154</v>
+      </c>
+      <c r="C78">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>52</v>
+      </c>
+      <c r="B79" t="s">
+        <v>155</v>
+      </c>
+      <c r="C79">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>53</v>
+      </c>
+      <c r="B80" t="s">
+        <v>156</v>
+      </c>
+      <c r="C80">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>54</v>
+      </c>
+      <c r="B81" t="s">
+        <v>157</v>
+      </c>
+      <c r="C81">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>55</v>
+      </c>
+      <c r="B82" t="s">
+        <v>158</v>
+      </c>
+      <c r="C82">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>56</v>
+      </c>
+      <c r="B83" t="s">
+        <v>159</v>
+      </c>
+      <c r="C83">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>57</v>
+      </c>
+      <c r="B84" t="s">
+        <v>160</v>
+      </c>
+      <c r="C84">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C85" s="3">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>3</v>
+      </c>
+      <c r="B86" t="s">
+        <v>186</v>
+      </c>
+      <c r="C86">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>162</v>
+      </c>
+      <c r="B87" t="s">
+        <v>187</v>
+      </c>
+      <c r="C87">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>88</v>
+      </c>
+      <c r="B88" t="s">
+        <v>188</v>
+      </c>
+      <c r="C88">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>89</v>
+      </c>
+      <c r="B89" s="4">
+        <v>64387</v>
+      </c>
+      <c r="C89">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>163</v>
+      </c>
+      <c r="B90" s="4">
+        <v>70730</v>
+      </c>
+      <c r="C90">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>164</v>
+      </c>
+      <c r="B91" t="s">
+        <v>189</v>
+      </c>
+      <c r="C91">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>165</v>
+      </c>
+      <c r="B92" t="s">
+        <v>190</v>
+      </c>
+      <c r="C92">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>166</v>
+      </c>
+      <c r="B93" t="s">
+        <v>191</v>
+      </c>
+      <c r="C93">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>167</v>
+      </c>
+      <c r="B94" t="s">
+        <v>192</v>
+      </c>
+      <c r="C94">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>168</v>
+      </c>
+      <c r="B95" s="4">
+        <v>73946</v>
+      </c>
+      <c r="C95">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>169</v>
+      </c>
+      <c r="B96" s="4">
+        <v>44845</v>
+      </c>
+      <c r="C96">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>170</v>
+      </c>
+      <c r="B97" s="4">
+        <v>41979</v>
+      </c>
+      <c r="C97">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>90</v>
+      </c>
+      <c r="B98" t="s">
+        <v>193</v>
+      </c>
+      <c r="C98">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>171</v>
+      </c>
+      <c r="B99" t="s">
+        <v>194</v>
+      </c>
+      <c r="C99">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>172</v>
+      </c>
+      <c r="B100" t="s">
+        <v>195</v>
+      </c>
+      <c r="C100">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>173</v>
+      </c>
+      <c r="B101" t="s">
+        <v>196</v>
+      </c>
+      <c r="C101">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>174</v>
+      </c>
+      <c r="B102" t="s">
+        <v>197</v>
+      </c>
+      <c r="C102">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>175</v>
+      </c>
+      <c r="B103" t="s">
+        <v>198</v>
+      </c>
+      <c r="C103">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>176</v>
+      </c>
+      <c r="B104" t="s">
+        <v>199</v>
+      </c>
+      <c r="C104">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>177</v>
+      </c>
+      <c r="B105" s="4">
+        <v>40937</v>
+      </c>
+      <c r="C105">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>178</v>
+      </c>
+      <c r="B106" s="4">
+        <v>34984</v>
+      </c>
+      <c r="C106">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>179</v>
+      </c>
+      <c r="B107" t="s">
+        <v>200</v>
+      </c>
+      <c r="C107">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>180</v>
+      </c>
+      <c r="B108" t="s">
+        <v>201</v>
+      </c>
+      <c r="C108">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>181</v>
+      </c>
+      <c r="B109" t="s">
+        <v>202</v>
+      </c>
+      <c r="C109">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>182</v>
+      </c>
+      <c r="B110" t="s">
+        <v>203</v>
+      </c>
+      <c r="C110">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>183</v>
+      </c>
+      <c r="B111" s="4">
+        <v>31135</v>
+      </c>
+      <c r="C111">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>184</v>
+      </c>
+      <c r="B112" t="s">
+        <v>205</v>
+      </c>
+      <c r="C112">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C113" s="3">
+        <v>2021</v>
       </c>
     </row>
   </sheetData>
@@ -1302,4 +2317,213 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EF0D4EF-ADFF-4CC2-8698-16CB9A197A3C}">
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="43.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="29" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" s="2">
+        <v>37940</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="29" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="29" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="29" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E7" s="2">
+        <v>37600</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="29" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="29" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="29" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="29" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="29" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D12" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" s="2">
+        <v>49600</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>114</v>
+      </c>
+      <c r="C13" t="s">
+        <v>115</v>
+      </c>
+      <c r="D13" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="29" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>112</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D14" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="29" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="29" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D16" t="s">
+        <v>121</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>